--- a/Desafio 4 - Vale Refeição/Desafio 4 - Dados - I2A2/ADMISSÃO ABRIL.xlsx
+++ b/Desafio 4 - Vale Refeição/Desafio 4 - Dados - I2A2/ADMISSÃO ABRIL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thais.agne\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Cursos e Treinamentos\Cientista de Dados\Treinamento Python\I2A2\Desafios\Desafio 4 - Vale Refeição\Desafio 4 - Dados - I2A2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3E7545-4567-43AD-BB36-27C28389A97A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB57FA7-D870-405F-98EF-F0175CEA11FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{B7FA0628-E6B4-4A82-A1AA-15812E6CCD74}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B7FA0628-E6B4-4A82-A1AA-15812E6CCD74}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -324,9 +327,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -364,7 +367,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -470,7 +473,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -612,7 +615,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -621,14 +624,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85476C61-8A42-48DE-AE21-636E21A42818}">
   <dimension ref="A1:D84"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.1796875" style="5"/>
+    <col min="1" max="1" width="10.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="5"/>
     <col min="3" max="3" width="26" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.1796875" style="5"/>
+    <col min="4" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -639,7 +643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>35741</v>
       </c>
@@ -650,7 +654,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>35774</v>
       </c>
@@ -661,7 +665,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>35722</v>
       </c>
@@ -672,7 +676,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>35767</v>
       </c>
@@ -683,7 +687,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>35701</v>
       </c>
@@ -694,7 +698,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>35770</v>
       </c>
@@ -705,7 +709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>35714</v>
       </c>
@@ -716,7 +720,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>35727</v>
       </c>
@@ -727,7 +731,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>35743</v>
       </c>
@@ -738,7 +742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>35782</v>
       </c>
@@ -749,7 +753,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>35726</v>
       </c>
@@ -760,7 +764,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>35769</v>
       </c>
@@ -771,7 +775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>35752</v>
       </c>
@@ -782,7 +786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>35738</v>
       </c>
@@ -793,7 +797,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>35740</v>
       </c>
@@ -804,7 +808,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>35702</v>
       </c>
@@ -815,7 +819,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>35706</v>
       </c>
@@ -826,7 +830,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>35734</v>
       </c>
@@ -837,7 +841,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>35747</v>
       </c>
@@ -848,7 +852,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7">
         <v>35708</v>
       </c>
@@ -862,7 +866,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>35780</v>
       </c>
@@ -873,7 +877,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>35720</v>
       </c>
@@ -884,7 +888,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>35737</v>
       </c>
@@ -895,7 +899,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>35704</v>
       </c>
@@ -906,7 +910,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>35748</v>
       </c>
@@ -917,7 +921,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>35781</v>
       </c>
@@ -928,7 +932,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>35773</v>
       </c>
@@ -939,7 +943,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>35724</v>
       </c>
@@ -950,7 +954,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>35746</v>
       </c>
@@ -961,7 +965,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>35763</v>
       </c>
@@ -972,7 +976,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>35756</v>
       </c>
@@ -983,7 +987,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>35758</v>
       </c>
@@ -994,7 +998,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>35718</v>
       </c>
@@ -1005,7 +1009,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>35730</v>
       </c>
@@ -1016,7 +1020,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35745</v>
       </c>
@@ -1027,7 +1031,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7">
         <v>35699</v>
       </c>
@@ -1041,7 +1045,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>35710</v>
       </c>
@@ -1052,7 +1056,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>35736</v>
       </c>
@@ -1063,7 +1067,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>35776</v>
       </c>
@@ -1074,7 +1078,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>35750</v>
       </c>
@@ -1085,7 +1089,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>35728</v>
       </c>
@@ -1096,7 +1100,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>35733</v>
       </c>
@@ -1107,7 +1111,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>35766</v>
       </c>
@@ -1118,7 +1122,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>35739</v>
       </c>
@@ -1129,7 +1133,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>35705</v>
       </c>
@@ -1140,7 +1144,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>35754</v>
       </c>
@@ -1151,7 +1155,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>35742</v>
       </c>
@@ -1162,7 +1166,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>35772</v>
       </c>
@@ -1173,7 +1177,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>35721</v>
       </c>
@@ -1184,7 +1188,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>35759</v>
       </c>
@@ -1195,7 +1199,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>35760</v>
       </c>
@@ -1206,7 +1210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>35723</v>
       </c>
@@ -1217,7 +1221,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>35707</v>
       </c>
@@ -1228,7 +1232,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>35749</v>
       </c>
@@ -1239,7 +1243,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>35713</v>
       </c>
@@ -1250,7 +1254,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>35753</v>
       </c>
@@ -1261,7 +1265,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>35717</v>
       </c>
@@ -1272,7 +1276,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>35716</v>
       </c>
@@ -1286,7 +1290,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>35768</v>
       </c>
@@ -1297,7 +1301,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>35777</v>
       </c>
@@ -1308,7 +1312,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>35725</v>
       </c>
@@ -1319,7 +1323,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>35771</v>
       </c>
@@ -1330,7 +1334,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>35715</v>
       </c>
@@ -1344,7 +1348,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>35783</v>
       </c>
@@ -1355,7 +1359,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>35700</v>
       </c>
@@ -1366,7 +1370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>35732</v>
       </c>
@@ -1377,7 +1381,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>35719</v>
       </c>
@@ -1391,7 +1395,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>35709</v>
       </c>
@@ -1402,7 +1406,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="7">
         <v>35755</v>
       </c>
@@ -1416,7 +1420,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>35712</v>
       </c>
@@ -1427,7 +1431,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>35778</v>
       </c>
@@ -1438,7 +1442,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>35761</v>
       </c>
@@ -1449,7 +1453,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>35762</v>
       </c>
@@ -1460,7 +1464,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>35775</v>
       </c>
@@ -1471,7 +1475,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>35764</v>
       </c>
@@ -1482,7 +1486,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>35731</v>
       </c>
@@ -1493,7 +1497,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>35729</v>
       </c>
@@ -1504,7 +1508,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>35703</v>
       </c>
@@ -1515,7 +1519,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>35711</v>
       </c>
@@ -1526,7 +1530,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>35779</v>
       </c>
@@ -1537,7 +1541,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>35744</v>
       </c>
@@ -1548,7 +1552,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>35765</v>
       </c>
@@ -1559,7 +1563,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>35751</v>
       </c>
